--- a/Result/profitability/6123.xlsx
+++ b/Result/profitability/6123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.97</v>
       </c>
       <c r="M2" t="n">
-        <v>0.78625</v>
+        <v>0.8125</v>
       </c>
       <c r="N2" t="n">
-        <v>14.425</v>
+        <v>14.53125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.72875</v>
+        <v>0.75875</v>
       </c>
       <c r="N3" t="n">
-        <v>15.1675</v>
+        <v>15.00125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7025</v>
+        <v>0.77625</v>
       </c>
       <c r="N4" t="n">
-        <v>15.68875</v>
+        <v>15.7125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66625</v>
+        <v>0.72625</v>
       </c>
       <c r="N5" t="n">
-        <v>15.99</v>
+        <v>15.94125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5924999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="N6" t="n">
-        <v>16.365</v>
+        <v>16.4975</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.52375</v>
+        <v>0.57875</v>
       </c>
       <c r="N7" t="n">
-        <v>16.9625</v>
+        <v>16.84875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5375</v>
+        <v>0.5975</v>
       </c>
       <c r="N8" t="n">
-        <v>17.305</v>
+        <v>17.37875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.99</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5075000000000001</v>
+        <v>0.5075</v>
       </c>
       <c r="N11" t="n">
         <v>18.25375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6123</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D75" t="n">
+        <v>934</v>
+      </c>
+      <c r="E75" t="n">
+        <v>152</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>107</v>
+      </c>
+      <c r="K75" t="n">
+        <v>71</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.9625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04409566517189845</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3899999999999988</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02715877437325898</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
